--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_Fiets.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_Fiets.xlsx
@@ -419,7 +419,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>89.07615236330427</v>
+        <v>89.07615236330426</v>
       </c>
       <c r="C4">
         <v>126.5733160212505</v>
@@ -456,7 +456,7 @@
         <v>68.18701711181139</v>
       </c>
       <c r="C6">
-        <v>93.43753236241514</v>
+        <v>93.43753236241513</v>
       </c>
       <c r="D6">
         <v>103.8763834122077</v>
@@ -470,7 +470,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>7.517089775047003</v>
+        <v>7.517089775047001</v>
       </c>
       <c r="C7">
         <v>10.21511999204041</v>
@@ -490,10 +490,10 @@
         <v>358.492594111587</v>
       </c>
       <c r="C8">
-        <v>499.9719941215532</v>
+        <v>499.9719941215529</v>
       </c>
       <c r="D8">
-        <v>573.809771499637</v>
+        <v>573.8097714996368</v>
       </c>
       <c r="E8">
         <v>613.0830182722573</v>
@@ -524,7 +524,7 @@
         <v>45.20527448267596</v>
       </c>
       <c r="C10">
-        <v>59.88081739165651</v>
+        <v>59.8808173916565</v>
       </c>
       <c r="D10">
         <v>66.24351636526342</v>
@@ -538,7 +538,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>8.235814857208368</v>
+        <v>8.235814857208366</v>
       </c>
       <c r="C11">
         <v>10.33906621362205</v>
@@ -578,7 +578,7 @@
         <v>33.24229471242814</v>
       </c>
       <c r="D13">
-        <v>37.0908174624488</v>
+        <v>37.09081746244878</v>
       </c>
       <c r="E13">
         <v>38.48114954406899</v>

--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_Fiets.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_Fiets.xlsx
@@ -385,16 +385,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>88.09512209212902</v>
+        <v>3.372062089650871</v>
       </c>
       <c r="C2">
-        <v>122.8752923687182</v>
+        <v>9.994641006067987</v>
       </c>
       <c r="D2">
-        <v>140.4649305349731</v>
+        <v>22.17867324236417</v>
       </c>
       <c r="E2">
-        <v>152.3759665483246</v>
+        <v>36.62883811257802</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>109.7616899675961</v>
+        <v>36.73656562180766</v>
       </c>
       <c r="C3">
-        <v>152.4139567022804</v>
+        <v>94.17447731197814</v>
       </c>
       <c r="D3">
-        <v>171.8865683428809</v>
+        <v>129.0903207146534</v>
       </c>
       <c r="E3">
-        <v>186.1018932339855</v>
+        <v>155.0849110283213</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>89.07615236330426</v>
+        <v>3.382638697340668</v>
       </c>
       <c r="C4">
-        <v>126.5733160212505</v>
+        <v>9.040951144375036</v>
       </c>
       <c r="D4">
-        <v>146.2030952735857</v>
+        <v>16.65604882863634</v>
       </c>
       <c r="E4">
-        <v>162.7257390116035</v>
+        <v>23.93025573700051</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -436,16 +436,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>78.332206316905</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>107.7504331296123</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>118.7076051509529</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>128.3091874784875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -453,16 +453,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>68.18701711181139</v>
+        <v>22.88794979976886</v>
       </c>
       <c r="C6">
-        <v>93.43753236241513</v>
+        <v>39.85796835040086</v>
       </c>
       <c r="D6">
-        <v>103.8763834122077</v>
+        <v>40.67886343415127</v>
       </c>
       <c r="E6">
-        <v>111.1853124387839</v>
+        <v>36.01777726890181</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>7.517089775047001</v>
+        <v>2.505696591682334</v>
       </c>
       <c r="C7">
-        <v>10.21511999204041</v>
+        <v>6.810079994693606</v>
       </c>
       <c r="D7">
-        <v>11.3728030142271</v>
+        <v>8.340055543766539</v>
       </c>
       <c r="E7">
-        <v>12.02350186905177</v>
+        <v>9.618801495241421</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -487,16 +487,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>358.492594111587</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>499.9719941215529</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>573.8097714996368</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>613.0830182722573</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>104.0122622924872</v>
+        <v>186.8181410107779</v>
       </c>
       <c r="C9">
-        <v>142.3326519684174</v>
+        <v>407.7452300351281</v>
       </c>
       <c r="D9">
-        <v>157.6476894685577</v>
+        <v>613.7545968630257</v>
       </c>
       <c r="E9">
-        <v>167.3080908080238</v>
+        <v>800.169129951418</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -521,16 +521,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>45.20527448267596</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>59.8808173916565</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>66.24351636526342</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>67.95026321152028</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>8.235814857208366</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>10.33906621362205</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>11.30501302485728</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>12.51877273516097</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>18.73786677604931</v>
+        <v>230.1394406596825</v>
       </c>
       <c r="C12">
-        <v>24.96752501600606</v>
+        <v>333.3164589636809</v>
       </c>
       <c r="D12">
-        <v>26.39180645040836</v>
+        <v>298.2274128896145</v>
       </c>
       <c r="E12">
-        <v>25.93710484873178</v>
+        <v>226.1183499633027</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -572,16 +572,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>25.34690985319946</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>33.24229471242814</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>37.09081746244878</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>38.48114954406899</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_Fiets.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_concproduct_Fiets.xlsx
@@ -385,16 +385,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>3.372062089650871</v>
+        <v>11.39433914485022</v>
       </c>
       <c r="C2">
-        <v>9.994641006067987</v>
+        <v>15.89285218661265</v>
       </c>
       <c r="D2">
-        <v>22.17867324236417</v>
+        <v>18.16791915901449</v>
       </c>
       <c r="E2">
-        <v>36.62883811257802</v>
+        <v>19.70850824816653</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>36.73656562180766</v>
+        <v>69.63496216885167</v>
       </c>
       <c r="C3">
-        <v>94.17447731197814</v>
+        <v>96.69439411967483</v>
       </c>
       <c r="D3">
-        <v>129.0903207146534</v>
+        <v>109.0481996717054</v>
       </c>
       <c r="E3">
-        <v>155.0849110283213</v>
+        <v>118.0666797197281</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>3.382638697340668</v>
+        <v>8.251264639969236</v>
       </c>
       <c r="C4">
-        <v>9.040951144375036</v>
+        <v>11.72468611565268</v>
       </c>
       <c r="D4">
-        <v>16.65604882863634</v>
+        <v>13.54302356218478</v>
       </c>
       <c r="E4">
-        <v>23.93025573700051</v>
+        <v>15.07354214002222</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -453,16 +453,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>22.88794979976886</v>
+        <v>25.19695378387426</v>
       </c>
       <c r="C6">
-        <v>39.85796835040086</v>
+        <v>34.52770460327424</v>
       </c>
       <c r="D6">
-        <v>40.67886343415127</v>
+        <v>38.38514343253209</v>
       </c>
       <c r="E6">
-        <v>36.01777726890181</v>
+        <v>41.08599111135446</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>2.505696591682334</v>
+        <v>4.760823524196434</v>
       </c>
       <c r="C7">
-        <v>6.810079994693606</v>
+        <v>6.469575994958926</v>
       </c>
       <c r="D7">
-        <v>8.340055543766539</v>
+        <v>7.202775242343826</v>
       </c>
       <c r="E7">
-        <v>9.618801495241421</v>
+        <v>7.614884517066123</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>186.8181410107779</v>
+        <v>346.9174123677991</v>
       </c>
       <c r="C9">
-        <v>407.7452300351281</v>
+        <v>474.7293658268643</v>
       </c>
       <c r="D9">
-        <v>613.7545968630257</v>
+        <v>525.8103928400444</v>
       </c>
       <c r="E9">
-        <v>800.169129951418</v>
+        <v>558.0312229734933</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>230.1394406596825</v>
+        <v>214.0623388023355</v>
       </c>
       <c r="C12">
-        <v>333.3164589636809</v>
+        <v>285.2302699613351</v>
       </c>
       <c r="D12">
-        <v>298.2274128896145</v>
+        <v>301.5013331834626</v>
       </c>
       <c r="E12">
-        <v>226.1183499633027</v>
+        <v>296.3067990630435</v>
       </c>
     </row>
     <row r="13" spans="1:5">
